--- a/output/graficos_otras_relaciones/plot_regional_d_otrasrel_a_2024_maule.xlsx
+++ b/output/graficos_otras_relaciones/plot_regional_d_otrasrel_a_2024_maule.xlsx
@@ -47,7 +47,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-06 17:14</t>
+    <t xml:space="preserve">2026-09-09 19:49</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_otras_relaciones/plot_regional_d_otrasrel_a_2024_maule.xlsx
+++ b/output/graficos_otras_relaciones/plot_regional_d_otrasrel_a_2024_maule.xlsx
@@ -47,7 +47,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-09 19:49</t>
+    <t xml:space="preserve">2026-09-17 04:12</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_otras_relaciones/plot_regional_d_otrasrel_a_2024_maule.xlsx
+++ b/output/graficos_otras_relaciones/plot_regional_d_otrasrel_a_2024_maule.xlsx
@@ -47,7 +47,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-17 04:12</t>
+    <t xml:space="preserve">2026-09-27 02:42</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_otras_relaciones/plot_regional_d_otrasrel_a_2024_maule.xlsx
+++ b/output/graficos_otras_relaciones/plot_regional_d_otrasrel_a_2024_maule.xlsx
@@ -47,7 +47,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-27 02:42</t>
+    <t xml:space="preserve">2026-10-03 02:17</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_otras_relaciones/plot_regional_d_otrasrel_a_2024_maule.xlsx
+++ b/output/graficos_otras_relaciones/plot_regional_d_otrasrel_a_2024_maule.xlsx
@@ -47,7 +47,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-03 02:17</t>
+    <t xml:space="preserve">2026-10-05 05:37</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
